--- a/public/asset/all_brands_items_ecommerce_catalog.xlsx
+++ b/public/asset/all_brands_items_ecommerce_catalog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\system\public\asset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{31D7DBB2-141A-4B05-9C8F-92B6FD0256B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AC2DAC2-07E8-46FE-A409-F9CA949983BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -819,7 +819,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <name val="Carlito"/>
@@ -834,6 +834,12 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Carlito"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Carlito"/>
     </font>
   </fonts>
@@ -864,10 +870,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -891,8 +898,10 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="1">
@@ -4798,7 +4807,7 @@
       <c r="C4" t="s">
         <v>241</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="9" t="s">
         <v>242</v>
       </c>
       <c r="E4" t="s">
@@ -4872,9 +4881,12 @@
   <mergeCells count="1">
     <mergeCell ref="A1:F1"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="D4" r:id="rId1" xr:uid="{5AB4F58F-F63E-46A7-BBF7-26EF78F5FA42}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
-    <tablePart r:id="rId1"/>
+    <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
 </file>
